--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M227"/>
+  <dimension ref="A1:M230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1456,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1521,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2163,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2610,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2675,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2740,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2805,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2870,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2935,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3000,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3065,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3191,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3317,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3382,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3447,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3634,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3882,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3947,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4012,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4077,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4203,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4268,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4333,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4398,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4463,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4528,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4593,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4658,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4723,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4788,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4853,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4979,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5166,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5231,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5296,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5361,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5426,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5491,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5556,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5621,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5686,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5812,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5938,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6003,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6068,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6133,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6198,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6263,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6328,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6393,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6519,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6584,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6771,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6897,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6614,7 +6914,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2292-725-CM25</t>
+          <t>2454-73-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6634,32 +6934,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.071.000-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6969,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>35735.7</v>
+        <v>20971.73</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2454-73-CM25</t>
+          <t>980313-158-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6695,48 +6995,52 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.071.000-5</t>
+          <t>69.250.900-5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUINTA NORMAL</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>20971.73</v>
+        <v>33051.06</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>980313-158-CM25</t>
+          <t>980313-157-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6776,28 +7080,32 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>33051.06</v>
+        <v>5222.48</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>980313-157-CM25</t>
+          <t>980313-156-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6837,12 +7145,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +7160,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5222.48</v>
+        <v>3562.86</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>980313-156-CM25</t>
+          <t>2409-642-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6883,12 +7191,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.250.900-5</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTUCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,28 +7206,32 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3562.86</v>
+        <v>16610.58</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2409-642-CM25</t>
+          <t>2409-641-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6959,12 +7271,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +7286,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>16610.58</v>
+        <v>26731.73</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2409-641-CM25</t>
+          <t>2409-640-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7020,28 +7332,32 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>26731.73</v>
+        <v>23230.51</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2409-640-CM25</t>
+          <t>188-465-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7066,43 +7382,47 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>23230.51</v>
+        <v>3865.12</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>188-465-CM25</t>
+          <t>2292-725-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,43 +7447,47 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3865.12</v>
+        <v>35735.7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4856-278-CM25</t>
+          <t>3507-452-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7188,43 +7512,47 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>5466</v>
+        <v>2249.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5965-147-CM25</t>
+          <t>4856-278-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7244,48 +7572,52 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>26829.74</v>
+        <v>5466</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3507-452-CM25</t>
+          <t>5965-147-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7305,42 +7637,46 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2249.1</v>
+        <v>26829.74</v>
       </c>
     </row>
     <row r="114">
@@ -7394,7 +7730,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7795,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7860,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7986,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8051,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8116,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8181,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8246,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8372,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8437,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8502,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8567,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8632,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8697,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8762,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8383,7 +8779,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2737-386-CM25</t>
+          <t>751-221-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8408,37 +8804,41 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>7082.95</v>
+        <v>2451.4</v>
       </c>
     </row>
     <row r="132">
@@ -8505,7 +8905,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>751-221-CM25</t>
+          <t>2737-386-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8530,37 +8930,41 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2451.4</v>
+        <v>7082.95</v>
       </c>
     </row>
     <row r="134">
@@ -8627,7 +9031,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4081-186-CM25</t>
+          <t>4594-526-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8652,37 +9056,41 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>14464.93</v>
+        <v>8497.530000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8736,7 +9144,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9209,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8871,7 +9287,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4594-526-CM25</t>
+          <t>4081-186-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8896,37 +9312,41 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>8497.530000000001</v>
+        <v>14464.93</v>
       </c>
     </row>
     <row r="140">
@@ -9041,7 +9461,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9526,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9591,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9176,7 +9608,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1213444-281-CM25</t>
+          <t>2306-666-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,48 +9628,52 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>14794.01</v>
+        <v>2751.18</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2306-666-CM25</t>
+          <t>1213444-281-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9257,42 +9693,46 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2751.18</v>
+        <v>14794.01</v>
       </c>
     </row>
     <row r="146">
@@ -9346,7 +9786,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9359,7 +9803,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>552975-546-CM25</t>
+          <t>2418-50-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9379,32 +9823,32 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.427.199-8</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9858,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4555.27</v>
+        <v>9377.200000000001</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2418-50-CM25</t>
+          <t>969221-10-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,43 +9889,47 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIAL FELP SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.427.199-8</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>9377.200000000001</v>
+        <v>8286.709999999999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>969221-10-CM25</t>
+          <t>2766-689-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9501,48 +9949,52 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.180.500-K</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8286.709999999999</v>
+        <v>13967.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2766-689-CM25</t>
+          <t>2409-706-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,43 +10019,47 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>13967.1</v>
+        <v>4018.51</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2409-706-CM25</t>
+          <t>2935-80-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9628,17 +10084,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.073.200-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE ALHUE</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9651,20 +10107,24 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4018.51</v>
+        <v>21864.01</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2935-80-CM25</t>
+          <t>612-4064-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9684,17 +10144,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.073.200-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALHUE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,28 +10164,32 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>21864.01</v>
+        <v>10353</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>612-4064-CM25</t>
+          <t>552975-546-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9745,17 +10209,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.070.301-7</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +10229,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,7 +10244,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>10353</v>
+        <v>4555.27</v>
       </c>
     </row>
     <row r="154">
@@ -9834,7 +10298,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10363,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10428,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10030,7 +10506,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3635-177-CM25</t>
+          <t>2324-886-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10055,43 +10531,47 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>7925.26</v>
+        <v>3705.66</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>881-201-CM25</t>
+          <t>3872-184-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10116,43 +10596,47 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2873.85</v>
+        <v>5960.71</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3872-184-CM25</t>
+          <t>3917-188-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,43 +10661,47 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>5960.71</v>
+        <v>30178.4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3917-188-CM25</t>
+          <t>3635-177-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10233,32 +10721,32 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,13 +10756,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>30178.4</v>
+        <v>7925.26</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2324-886-CM25</t>
+          <t>3917-189-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10294,48 +10782,52 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3705.66</v>
+        <v>14732.2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3917-189-CM25</t>
+          <t>2294-1272-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10355,32 +10847,32 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10882,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>14732.2</v>
+        <v>2413.32</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2294-1272-CM25</t>
+          <t>2789-247-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10416,48 +10908,52 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2413.32</v>
+        <v>3776.99</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2789-247-CM25</t>
+          <t>881-201-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10482,43 +10978,47 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3776.99</v>
+        <v>2873.85</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>881-200-CM25</t>
+          <t>2294-1269-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10538,48 +11038,52 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>15628.27</v>
+        <v>2946.44</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2294-1269-CM25</t>
+          <t>881-200-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10599,42 +11103,46 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2946.44</v>
+        <v>15628.27</v>
       </c>
     </row>
     <row r="168">
@@ -10688,7 +11196,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10701,7 +11213,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4171-479-CM25</t>
+          <t>2733-360-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,37 +11238,41 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>70.834.500-8</t>
+          <t>69.071.700-K</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>13588.38</v>
+        <v>14732.2</v>
       </c>
     </row>
     <row r="170">
@@ -10823,7 +11339,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2817-457-CM25</t>
+          <t>4406-411-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10848,27 +11364,27 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +11394,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>16919.42</v>
+        <v>3240.7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2409-710-CM25</t>
+          <t>836-121-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10904,48 +11420,52 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>11428.52</v>
+        <v>30372.37</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4014-376-CM25</t>
+          <t>3826-249-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10970,27 +11490,27 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,13 +11520,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>34986</v>
+        <v>7157.73</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4014-377-CM25</t>
+          <t>4014-378-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11046,28 +11566,32 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>28532.27</v>
+        <v>35184.78</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2733-360-CM25</t>
+          <t>4014-377-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11087,48 +11611,52 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.071.700-K</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>14732.2</v>
+        <v>28532.27</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3826-249-CM25</t>
+          <t>4014-376-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11153,43 +11681,47 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>7157.73</v>
+        <v>34986</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>836-121-CM25</t>
+          <t>2409-710-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11209,48 +11741,52 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>30372.37</v>
+        <v>11428.52</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4406-411-CM25</t>
+          <t>2817-457-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11275,43 +11811,47 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Lumaco</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3240.7</v>
+        <v>16919.42</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4014-378-CM25</t>
+          <t>4171-479-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11331,48 +11871,52 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>70.834.500-8</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>35184.78</v>
+        <v>13588.38</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2332-658-CM25</t>
+          <t>5890-58-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11397,43 +11941,47 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>6241.79</v>
+        <v>41929.75</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>691791-8-CM25</t>
+          <t>612-4070-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11458,12 +12006,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11473,28 +12021,32 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>70670.72</v>
+        <v>5105.1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1736-3157-CM25</t>
+          <t>2277-54-SE25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11514,17 +12066,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.255.300-4</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,22 +12086,26 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2933.49</v>
+        <v>6688.63</v>
       </c>
     </row>
     <row r="183">
@@ -11616,7 +12172,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>612-4070-CM25</t>
+          <t>1028897-766-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11641,43 +12197,47 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>5105.1</v>
+        <v>2470.34</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5890-58-CM25</t>
+          <t>691791-8-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11702,12 +12262,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11717,28 +12277,32 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>41929.75</v>
+        <v>70670.72</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2799-535-CM25</t>
+          <t>2332-658-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11763,43 +12327,47 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2350.13</v>
+        <v>6241.79</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1028897-766-CM25</t>
+          <t>1736-3157-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11824,17 +12392,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>69.255.300-4</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11847,20 +12415,24 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2470.34</v>
+        <v>2933.49</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2324-889-CM25</t>
+          <t>2799-535-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11880,32 +12452,32 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +12487,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>10956.19</v>
+        <v>2350.13</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4469-436-CM25</t>
+          <t>2277-53-SE25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11946,43 +12518,47 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>4374.11</v>
+        <v>70643.52</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4469-435-CM25</t>
+          <t>2324-889-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12007,43 +12583,47 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2932.02</v>
+        <v>10956.19</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4455-415-CM25</t>
+          <t>4469-436-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12063,48 +12643,52 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>6042.59</v>
+        <v>4374.11</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3110-126-CM25</t>
+          <t>4469-435-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12124,17 +12708,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.102.033-3</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,28 +12728,32 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2656.08</v>
+        <v>2932.02</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2791-176-CM25</t>
+          <t>4455-415-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12185,32 +12773,32 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12220,13 +12808,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>3834.18</v>
+        <v>6042.59</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5403-39-CM25</t>
+          <t>3110-126-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12251,27 +12839,27 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>61.102.033-3</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,13 +12869,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>7366.1</v>
+        <v>2656.08</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5148-84-CM25</t>
+          <t>4467-3-CC25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12307,17 +12895,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12327,28 +12915,32 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>21931.33</v>
+        <v>27637.37</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2378-75-CM25</t>
+          <t>2791-176-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12363,22 +12955,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.070.700-4</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12407,13 +12999,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>102498.75</v>
+        <v>3834.18</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2294-1299-CM25</t>
+          <t>5403-39-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12428,53 +13020,57 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>28484.02</v>
+        <v>7366.1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2789-252-CM25</t>
+          <t>5148-84-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12489,7 +13085,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12499,12 +13095,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12514,28 +13110,32 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>6967.93</v>
+        <v>21931.33</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4364-277-CM25</t>
+          <t>2378-75-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12555,42 +13155,46 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.070.700-4</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>10918.73</v>
+        <v>102498.75</v>
       </c>
     </row>
     <row r="200">
@@ -12644,7 +13248,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12657,7 +13265,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2687-124-CM25</t>
+          <t>2294-1299-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12677,32 +13285,32 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12712,13 +13320,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2820.23</v>
+        <v>28484.02</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1394-212-CM25</t>
+          <t>4364-277-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12738,48 +13346,52 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>6414.1</v>
+        <v>10918.73</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5514-29-CM25</t>
+          <t>2789-252-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12799,32 +13411,32 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12834,13 +13446,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>6711.6</v>
+        <v>6967.93</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2324-903-CM25</t>
+          <t>2687-124-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12860,32 +13472,32 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.596.570-5</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12895,13 +13507,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>10995.6</v>
+        <v>2820.23</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2800-118-CM25</t>
+          <t>1394-212-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12916,53 +13528,57 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>12495</v>
+        <v>6414.1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1077499-77-CM25</t>
+          <t>5514-29-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12977,53 +13593,57 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>11868.74</v>
+        <v>6711.6</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1110404-743-CM25</t>
+          <t>2324-903-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13038,53 +13658,57 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>4669.35</v>
+        <v>10995.6</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4451-385-CM25</t>
+          <t>2800-118-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13104,48 +13728,52 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>16392.01</v>
+        <v>12495</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1736-3172-CM25</t>
+          <t>1658-3228-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13165,48 +13793,52 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.255.300-4</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>29923.31</v>
+        <v>23019.36</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1057831-7-CM25</t>
+          <t>1216062-451-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13226,42 +13858,46 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>10565.86</v>
+        <v>35765.87</v>
       </c>
     </row>
     <row r="211">
@@ -13328,7 +13964,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1216062-451-CM25</t>
+          <t>1057831-7-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13348,48 +13984,52 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>35765.87</v>
+        <v>10565.86</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1658-3228-CM25</t>
+          <t>4034-385-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13414,43 +14054,47 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>23019.36</v>
+        <v>31861.18</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4034-385-CM25</t>
+          <t>1736-3172-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13470,32 +14114,32 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>69.255.300-4</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13505,13 +14149,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>31861.18</v>
+        <v>29923.31</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5178-2979-CM25</t>
+          <t>4451-385-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13526,7 +14170,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13536,17 +14180,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13559,20 +14203,24 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>11387.68</v>
+        <v>16392.01</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>948354-791-CM25</t>
+          <t>1110404-743-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13587,7 +14235,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13597,43 +14245,47 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>71310.75</v>
+        <v>4669.35</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>4563-60-CM25</t>
+          <t>1077499-77-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13648,47 +14300,51 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>6807.04</v>
+        <v>11868.74</v>
       </c>
     </row>
     <row r="218">
@@ -13755,7 +14411,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1058900-52-CM25</t>
+          <t>5178-2979-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13780,43 +14436,47 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2470.15</v>
+        <v>11387.68</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>697202-39-CM25</t>
+          <t>948354-791-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13841,43 +14501,47 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3188.61</v>
+        <v>71310.75</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4549-163-CM25</t>
+          <t>4563-60-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13902,43 +14566,47 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4165</v>
+        <v>6807.04</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4549-161-CM25</t>
+          <t>1058900-52-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13958,48 +14626,52 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>5312.16</v>
+        <v>2470.15</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4549-159-CM25</t>
+          <t>697202-39-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14019,17 +14691,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14039,28 +14711,32 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>8181.25</v>
+        <v>3188.61</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>711841-370-CM25</t>
+          <t>4549-163-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14080,48 +14756,52 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>20740.99</v>
+        <v>4165</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>552975-509-CM25</t>
+          <t>4549-161-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14146,47 +14826,43 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>34008.01</v>
+        <v>5312.16</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1110404-745-CM25</t>
+          <t>4549-159-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14206,32 +14882,32 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14241,67 +14917,266 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>10955.5</v>
+        <v>8181.25</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
+          <t>711841-370-CM25</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>60.103.000-4</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="n">
+        <v>20740.99</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>552975-509-CM25</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>69.070.301-7</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="n">
+        <v>34008.01</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1110404-745-CM25</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="n">
+        <v>10955.5</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
           <t>1110404-764-CM25</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>2239-1-LR24</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>jun-2025</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>62.000.660-2</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
+      <c r="H230" t="inlineStr">
         <is>
           <t>Arica y Parinacota</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
+      <c r="I230" t="inlineStr">
         <is>
           <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr">
+      <c r="J230" t="inlineStr">
         <is>
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M227" s="2" t="n">
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="n">
         <v>9133.49</v>
       </c>
     </row>
